--- a/outputs/Block2_National_Final_Tuning_v12.xlsx
+++ b/outputs/Block2_National_Final_Tuning_v12.xlsx
@@ -495,7 +495,7 @@
         <v>22</v>
       </c>
       <c r="F2">
-        <v>0.02325119999999976</v>
+        <v>0.02325119999999975</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
@@ -564,7 +564,7 @@
         <v>22</v>
       </c>
       <c r="F5">
-        <v>0.02322919999999977</v>
+        <v>0.02322919999999976</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
@@ -633,7 +633,7 @@
         <v>22</v>
       </c>
       <c r="F8">
-        <v>0.03054480000000005</v>
+        <v>0.03054480000000003</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
@@ -702,7 +702,7 @@
         <v>22</v>
       </c>
       <c r="F11">
-        <v>0.03134800000000005</v>
+        <v>0.03134800000000004</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>

--- a/outputs/Block2_National_Final_Tuning_v12.xlsx
+++ b/outputs/Block2_National_Final_Tuning_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="25">
   <si>
     <t>Stage</t>
   </si>
@@ -83,12 +83,6 @@
   </si>
   <si>
     <t>Popular Vote</t>
-  </si>
-  <si>
-    <t>House Buckets</t>
-  </si>
-  <si>
-    <t>Senate Buckets</t>
   </si>
   <si>
     <t>Mean target MAE in native units</t>
@@ -452,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -495,10 +489,10 @@
         <v>22</v>
       </c>
       <c r="F2">
-        <v>0.02325119999999975</v>
+        <v>0.02240799999999981</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -509,19 +503,19 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>0.02155479999999969</v>
+      </c>
+      <c r="G3" t="s">
         <v>23</v>
-      </c>
-      <c r="F3">
-        <v>5.3971</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -529,7 +523,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -538,13 +532,13 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>1.031</v>
+        <v>0.02860559999999995</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -552,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -564,10 +558,10 @@
         <v>22</v>
       </c>
       <c r="F5">
-        <v>0.02322919999999976</v>
+        <v>0.02842240000000001</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -575,22 +569,22 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>0.02191837617006417</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6">
-        <v>5.562900000000001</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -598,22 +592,22 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>1.0378</v>
+        <v>0.02139624692672173</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -621,22 +615,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
       </c>
       <c r="F8">
-        <v>0.03054480000000003</v>
+        <v>0.02974455870693945</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -644,22 +638,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>5.785300000000001</v>
+        <v>8.020000000000001</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -667,22 +661,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10">
+        <v>4.279249385344345</v>
+      </c>
+      <c r="G10" t="s">
         <v>24</v>
-      </c>
-      <c r="F10">
-        <v>1.1625</v>
-      </c>
-      <c r="G10" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -690,22 +684,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
       </c>
       <c r="F11">
-        <v>0.03134800000000004</v>
+        <v>4.766301551609027</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -713,22 +707,22 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>5.867500000000001</v>
+        <v>2.259284845582338</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -736,344 +730,22 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13">
+        <v>2.259284845582338</v>
+      </c>
+      <c r="G13" t="s">
         <v>24</v>
-      </c>
-      <c r="F13">
-        <v>1.1751</v>
-      </c>
-      <c r="G13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14">
-        <v>0.01607482587550967</v>
-      </c>
-      <c r="G14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15">
-        <v>5.067919260087908</v>
-      </c>
-      <c r="G15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16">
-        <v>1.013017383303414</v>
-      </c>
-      <c r="G16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17">
-        <v>0.01631950243820794</v>
-      </c>
-      <c r="G17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18">
-        <v>4.997511551750367</v>
-      </c>
-      <c r="G18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19">
-        <v>1.005925204663541</v>
-      </c>
-      <c r="G19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20">
-        <v>0.02329991933866525</v>
-      </c>
-      <c r="G20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21">
-        <v>5.144241398787647</v>
-      </c>
-      <c r="G21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22">
-        <v>1.046816049554921</v>
-      </c>
-      <c r="G22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23">
-        <v>8.020000000000001</v>
-      </c>
-      <c r="G23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24">
-        <v>3.214965175101933</v>
-      </c>
-      <c r="G24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25">
-        <v>5.2778760639537</v>
-      </c>
-      <c r="G25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26">
-        <v>2.259284845582338</v>
-      </c>
-      <c r="G26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27">
-        <v>2.259284845582338</v>
-      </c>
-      <c r="G27" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_National_Final_Tuning_v12.xlsx
+++ b/outputs/Block2_National_Final_Tuning_v12.xlsx
@@ -535,7 +535,7 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>0.02860559999999995</v>
+        <v>0.02860559999999996</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>

--- a/outputs/Block2_National_Final_Tuning_v12.xlsx
+++ b/outputs/Block2_National_Final_Tuning_v12.xlsx
@@ -535,7 +535,7 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>0.02860559999999996</v>
+        <v>0.02860559999999995</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -558,7 +558,7 @@
         <v>22</v>
       </c>
       <c r="F5">
-        <v>0.02842240000000001</v>
+        <v>0.02842240000000002</v>
       </c>
       <c r="G5" t="s">
         <v>23</v>
@@ -696,7 +696,7 @@
         <v>22</v>
       </c>
       <c r="F11">
-        <v>4.766301551609027</v>
+        <v>4.766301551609024</v>
       </c>
       <c r="G11" t="s">
         <v>24</v>

--- a/outputs/Block2_National_Final_Tuning_v12.xlsx
+++ b/outputs/Block2_National_Final_Tuning_v12.xlsx
@@ -535,7 +535,7 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>0.02860559999999995</v>
+        <v>0.02860559999999996</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -558,7 +558,7 @@
         <v>22</v>
       </c>
       <c r="F5">
-        <v>0.02842240000000002</v>
+        <v>0.02842240000000001</v>
       </c>
       <c r="G5" t="s">
         <v>23</v>
@@ -696,7 +696,7 @@
         <v>22</v>
       </c>
       <c r="F11">
-        <v>4.766301551609024</v>
+        <v>4.766301551609027</v>
       </c>
       <c r="G11" t="s">
         <v>24</v>

--- a/outputs/Block2_National_Final_Tuning_v12.xlsx
+++ b/outputs/Block2_National_Final_Tuning_v12.xlsx
@@ -489,7 +489,7 @@
         <v>22</v>
       </c>
       <c r="F2">
-        <v>0.02240799999999981</v>
+        <v>0.02240799999999982</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
@@ -535,7 +535,7 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>0.02860559999999996</v>
+        <v>0.02860559999999995</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>

--- a/outputs/Block2_National_Final_Tuning_v12.xlsx
+++ b/outputs/Block2_National_Final_Tuning_v12.xlsx
@@ -489,7 +489,7 @@
         <v>22</v>
       </c>
       <c r="F2">
-        <v>0.02240799999999982</v>
+        <v>0.02240799999999981</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
